--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484655_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484655_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1289</v>
+        <v>2.6808</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1904</v>
+        <v>0.9404</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9386</v>
+        <v>1.7404</v>
       </c>
       <c r="G2" t="n">
         <v>0.5024</v>
@@ -610,13 +610,13 @@
         <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5428</v>
+        <v>1.0946</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9766</v>
+        <v>0.7266</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5662</v>
+        <v>0.368</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0435</v>
+        <v>2.5079</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6059</v>
+        <v>2.0455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4376</v>
+        <v>0.4624</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3236</v>
@@ -688,13 +688,13 @@
         <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4051</v>
+        <v>0.0594</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3657</v>
+        <v>0.3904</v>
       </c>
       <c r="V3" t="n">
         <v>2.8559</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7963</v>
+        <v>1.8681</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9214</v>
+        <v>1.1573</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7177</v>
+        <v>0.7108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4011</v>
+        <v>1.1628</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3233</v>
+        <v>0.8905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7244</v>
+        <v>0.2723</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.177</v>
+        <v>2.7308</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2604</v>
+        <v>1.9133</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0833</v>
+        <v>0.8176</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5781</v>
+        <v>-1.568</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9371</v>
+        <v>-1.0228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.641</v>
+        <v>-0.5452</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8455</v>
+        <v>0.2838</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2557</v>
+        <v>-0.3458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5898</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.648</v>
+        <v>1.3365</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0611</v>
+        <v>0.3709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5869</v>
+        <v>0.9656</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1628</v>
+        <v>0.8273</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8905</v>
+        <v>-0.5899</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2723</v>
+        <v>1.4172</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7308</v>
+        <v>1.9619</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9133</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8176</v>
+        <v>1.9625</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.568</v>
+        <v>-1.1345</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0228</v>
+        <v>-0.5893</v>
       </c>
       <c r="O5" t="n">
         <v>-0.5452</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4419</v>
+        <v>-0.0803</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5056</v>
+        <v>0.066</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3115</v>
+        <v>1.2566</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7779</v>
+        <v>1.3315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6929999999999999</v>
+        <v>-1.1137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0848</v>
+        <v>2.4452</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.637</v>
+        <v>0.4011</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5727</v>
+        <v>-0.3233</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0643</v>
+        <v>0.7244</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0867</v>
+        <v>-1.177</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0867</v>
+        <v>-1.2604</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7237</v>
+        <v>1.5781</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6594</v>
+        <v>0.9371</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0643</v>
+        <v>0.641</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5851</v>
+        <v>0.3807</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6606</v>
+        <v>0.0634</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0755</v>
+        <v>0.3173</v>
       </c>
       <c r="V6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7012</v>
+        <v>1.2893</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0825</v>
+        <v>0.9815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6188</v>
+        <v>0.3078</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8273</v>
+        <v>-0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5899</v>
+        <v>-0.5727</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4172</v>
+        <v>-0.0643</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9619</v>
+        <v>0.0867</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0867</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9625</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1345</v>
+        <v>-0.7237</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5893</v>
+        <v>-0.6594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5452</v>
+        <v>-0.0643</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.733</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6496</v>
+        <v>-0.0737</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3688</v>
+        <v>-0.3722</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2809</v>
+        <v>0.2984</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2566</v>
+        <v>1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1005</v>
+        <v>-0.5877</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3983</v>
+        <v>-0.8154</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2978</v>
+        <v>0.2277</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0623</v>
+        <v>0.0492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2458</v>
+        <v>0.1679</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3081</v>
+        <v>-0.1187</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1788</v>
+        <v>0.0417</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6532</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4743</v>
+        <v>0.0417</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2412</v>
+        <v>0.0075</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4074</v>
+        <v>0.1679</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8338</v>
+        <v>-0.1603</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8617</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.73</v>
+        <v>0.0592</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1316</v>
+        <v>0.0369</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.838</v>
+        <v>-0.6103</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9666</v>
+        <v>-0.6048</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1287</v>
+        <v>-0.0055</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0492</v>
+        <v>-0.2484</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1679</v>
+        <v>-0.1392</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1187</v>
+        <v>-0.1091</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0417</v>
+        <v>0.17</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0867</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417</v>
+        <v>0.0833</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0075</v>
+        <v>-0.4184</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1679</v>
+        <v>-0.2259</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1603</v>
+        <v>-0.1925</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1541</v>
+        <v>0.0045</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.092</v>
+        <v>0.1414</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0621</v>
+        <v>-0.1369</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1025</v>
+        <v>-1.0101</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9483</v>
+        <v>-0.3159</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1542</v>
+        <v>-0.6942</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2484</v>
+        <v>-1.0623</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1392</v>
+        <v>0.2458</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1091</v>
+        <v>-1.3081</v>
       </c>
       <c r="J10" t="n">
-        <v>0.17</v>
+        <v>1.1788</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0867</v>
+        <v>1.6532</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0833</v>
+        <v>-0.4743</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4184</v>
+        <v>-2.2412</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2259</v>
+        <v>-1.4074</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1925</v>
+        <v>-0.8338</v>
       </c>
       <c r="P10" t="n">
         <v>-0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4876</v>
+        <v>0.7511</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2021</v>
+        <v>0.0159</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2855</v>
+        <v>0.7353</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1015</v>
+        <v>-1.9255</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5201</v>
+        <v>-0.3688</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5814</v>
+        <v>-1.5566</v>
       </c>
       <c r="G11" t="n">
         <v>0.1332</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1667</v>
+        <v>0.0092</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1666</v>
+        <v>-0.0154</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0001</v>
+        <v>0.0247</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1674</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7409</v>
+        <v>-2.2194</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8495</v>
+        <v>-2.0803</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1086</v>
+        <v>-0.1391</v>
       </c>
       <c r="G12" t="n">
         <v>0.164</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2006</v>
+        <v>0.3209</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.1304</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.4513</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.267</v>
+        <v>-7.2393</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2884</v>
+        <v>-4.3845</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9786</v>
+        <v>-2.8547</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8149</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2651</v>
+        <v>0.2928</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0196</v>
+        <v>-0.1157</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2847</v>
+        <v>0.4085</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5339</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.853599999999999</v>
+        <v>-2.578199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4631</v>
+        <v>-4.187799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.609699999999999</v>
+        <v>1.6098</v>
       </c>
       <c r="G14" t="n">
         <v>-4.8462</v>
@@ -1519,7 +1519,7 @@
         <v>-2.0837</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7970999999999999</v>
+        <v>0.7971000000000008</v>
       </c>
       <c r="K14" t="n">
         <v>1.1155</v>
@@ -1546,19 +1546,19 @@
         <v>10.9954</v>
       </c>
       <c r="S14" t="n">
-        <v>2.93</v>
+        <v>3.2052</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6597000000000001</v>
+        <v>-0.3844</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5896</v>
+        <v>3.5894</v>
       </c>
       <c r="V14" t="n">
         <v>-0.02060000000000084</v>
       </c>
       <c r="W14" t="n">
-        <v>7.311099999999999</v>
+        <v>7.311100000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.3319</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.024900000000001</v>
+        <v>8.401400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4012</v>
+        <v>4.7282</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6236</v>
+        <v>3.6732</v>
       </c>
       <c r="G15" t="n">
         <v>4.7801</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7842</v>
+        <v>0.1606</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3266</v>
+        <v>-0.3465</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4576</v>
+        <v>0.5071</v>
       </c>
       <c r="V15" t="n">
         <v>2.5444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1839</v>
+        <v>5.6192</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6861</v>
+        <v>4.0352</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4978</v>
+        <v>1.584</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5589</v>
+        <v>3.5033</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3056</v>
+        <v>1.2659</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2533</v>
+        <v>2.2374</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0972</v>
+        <v>3.3633</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6128</v>
+        <v>1.2538</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4844</v>
+        <v>2.1095</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4617</v>
+        <v>0.14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6928</v>
+        <v>0.0121</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7689</v>
+        <v>0.1279</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
         <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3304</v>
+        <v>-0.3343</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9004</v>
+        <v>-0.6342</v>
       </c>
       <c r="U16" t="n">
-        <v>0.57</v>
+        <v>0.2999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5889</v>
+        <v>1.9005</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>2.2224</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6911</v>
+        <v>5.3776</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4583</v>
+        <v>1.9746</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2329</v>
+        <v>3.403</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5033</v>
+        <v>3.5589</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2659</v>
+        <v>1.3056</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2374</v>
+        <v>2.2533</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3633</v>
+        <v>2.0972</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2538</v>
+        <v>0.6128</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1095</v>
+        <v>1.4844</v>
       </c>
       <c r="M17" t="n">
-        <v>0.14</v>
+        <v>1.4617</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0121</v>
+        <v>0.6928</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1279</v>
+        <v>0.7689</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
         <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2624</v>
+        <v>-0.1367</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2111</v>
+        <v>-0.612</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0512</v>
+        <v>0.4753</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9005</v>
+        <v>1.5889</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2224</v>
+        <v>1.5889</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3988</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6062</v>
+        <v>-1.3177</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2074</v>
+        <v>1.2365</v>
       </c>
       <c r="G18" t="n">
         <v>0.1795</v>
@@ -1858,13 +1858,13 @@
         <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6882</v>
+        <v>-0.3707</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6056</v>
+        <v>-0.3171</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0827</v>
+        <v>-0.0536</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6231</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7964</v>
+        <v>-1.184</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2011</v>
+        <v>-1.4896</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4047</v>
+        <v>0.3056</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0055</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7039</v>
+        <v>0.3164</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0392</v>
+        <v>-0.3276</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7431</v>
+        <v>0.644</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3115</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6664</v>
+        <v>-2.0394</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4055</v>
+        <v>-1.8863</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2609</v>
+        <v>-0.1531</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7302999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4695</v>
+        <v>0.0965</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2911</v>
+        <v>-0.1896</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1784</v>
+        <v>0.2862</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5889</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4306</v>
+        <v>-2.2063</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0743</v>
+        <v>-1.9781</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3563</v>
+        <v>-0.2281</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3206</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4216</v>
+        <v>-0.1972</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0188</v>
+        <v>0.1471</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5238</v>
+        <v>-2.6097</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-1.1498</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6624</v>
+        <v>-1.4599</v>
       </c>
       <c r="G22" t="n">
         <v>-0.243</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.464</v>
+        <v>-0.55</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0196</v>
+        <v>-0.3081</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4444</v>
+        <v>-0.2419</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5654</v>
+        <v>-3.3906</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5245</v>
+        <v>-2.4283</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.041</v>
+        <v>-0.9623</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7995</v>
@@ -2248,13 +2248,13 @@
         <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3445</v>
+        <v>-0.1697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0142</v>
+        <v>0.0645</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6651</v>
+        <v>-3.7516</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4825</v>
+        <v>-2.0979</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1826</v>
+        <v>-1.6537</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0767</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3764</v>
+        <v>-0.4629</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6606</v>
+        <v>-0.276</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7158</v>
+        <v>-0.1869</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5785</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.853400000000001</v>
+        <v>4.1354</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.609900000000002</v>
+        <v>-1.609699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4.4632</v>
+        <v>5.745200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>4.8462</v>
@@ -2377,13 +2377,13 @@
         <v>2.0838</v>
       </c>
       <c r="J25" t="n">
-        <v>5.6433</v>
+        <v>5.643300000000002</v>
       </c>
       <c r="K25" t="n">
         <v>3.8778</v>
       </c>
       <c r="L25" t="n">
-        <v>1.7656</v>
+        <v>1.765600000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-0.7970999999999998</v>
@@ -2404,13 +2404,13 @@
         <v>11.9118</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9299</v>
+        <v>-1.648</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.5895</v>
+        <v>-3.5896</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6596</v>
+        <v>1.9417</v>
       </c>
       <c r="V25" t="n">
         <v>0.02100000000000013</v>
